--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-biobank-biosafety-level.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-biobank-biosafety-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:13:27+00:00</t>
+    <t>2026-09-02T09:37:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-biobank-biosafety-level.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-biobank-biosafety-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:37:04+00:00</t>
+    <t>2026-09-02T10:26:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-biobank-biosafety-level.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/ValueSet-mii-vs-biobank-biosafety-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:26:48+00:00</t>
+    <t>2026-09-02T10:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
